--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -725,15 +725,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B13"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="29" min="1" max="1"/>
     <col width="108" customWidth="1" style="29" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="30">
       <c r="B2" s="31" t="inlineStr">
         <is>
@@ -748,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="30">
       <c r="B5" s="33" t="inlineStr">
         <is>
@@ -776,6 +778,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="30">
       <c r="B10" s="33" t="inlineStr">
         <is>
@@ -790,6 +793,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="39" customHeight="1" s="30">
       <c r="B13" s="35" t="inlineStr">
         <is>
@@ -797,10 +801,37 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -808,7 +839,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1337,9 +1368,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1347,7 +1378,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1372,6 +1403,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="30">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -1518,9 +1550,9 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1528,9 +1560,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="29" min="1" max="1"/>
@@ -1553,6 +1585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="30">
       <c r="A4" s="38" t="inlineStr">
         <is>
@@ -1620,6 +1653,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="30">
       <c r="A10" s="49" t="inlineStr">
         <is>
@@ -1675,6 +1709,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="22.35" customHeight="1" s="30">
       <c r="A16" s="58" t="inlineStr">
         <is>
@@ -1682,6 +1717,30 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
@@ -1716,9 +1775,9 @@
       <formula2>0.999</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -183,8 +183,17 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +242,11 @@
         <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -268,7 +282,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -444,6 +458,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,6 +537,124 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Sample size against margin of error</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Sample needed</v>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sample size calculator'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sample size calculator'!$B$37:$B$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Contacts to sample</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -544,6 +683,33 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1403,7 +1569,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="30">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -1562,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="29" min="1" max="1"/>
@@ -1720,27 +1885,222 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
+    <row r="20">
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>How sample size moves with the precision you ask for</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>Worst-case proportion (p=0.5), 95% confidence. Halving the margin of error costs you four times the sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="61" t="inlineStr">
+        <is>
+          <t>Margin of error</t>
+        </is>
+      </c>
+      <c r="B22" s="61" t="inlineStr">
+        <is>
+          <t>Sample needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B23" s="63">
+        <f>CEILING(1.96^2*0.25/A23^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="B24" s="63">
+        <f>CEILING(1.96^2*0.25/A24^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B25" s="63">
+        <f>CEILING(1.96^2*0.25/A25^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="B26" s="63">
+        <f>CEILING(1.96^2*0.25/A26^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B27" s="63">
+        <f>CEILING(1.96^2*0.25/A27^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="B28" s="63">
+        <f>CEILING(1.96^2*0.25/A28^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B29" s="63">
+        <f>CEILING(1.96^2*0.25/A29^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="B30" s="63">
+        <f>CEILING(1.96^2*0.25/A30^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B31" s="63">
+        <f>CEILING(1.96^2*0.25/A31^2,1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="32"/>
     <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
+    <row r="34">
+      <c r="A34" s="59" t="inlineStr">
+        <is>
+          <t>How sample size moves with the precision you ask for</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Worst-case proportion (p=0.5), 95% confidence. Halving the margin of error costs you four times the sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="61" t="inlineStr">
+        <is>
+          <t>Margin of error</t>
+        </is>
+      </c>
+      <c r="B36" s="61" t="inlineStr">
+        <is>
+          <t>Sample needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B37" s="63">
+        <f>CEILING(1.96^2*0.25/A37^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="62" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="B38" s="63">
+        <f>CEILING(1.96^2*0.25/A38^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B39" s="63">
+        <f>CEILING(1.96^2*0.25/A39^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="B40" s="63">
+        <f>CEILING(1.96^2*0.25/A40^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="62" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B41" s="63">
+        <f>CEILING(1.96^2*0.25/A41^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="62" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="B42" s="63">
+        <f>CEILING(1.96^2*0.25/A42^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B43" s="63">
+        <f>CEILING(1.96^2*0.25/A43^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="62" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="B44" s="63">
+        <f>CEILING(1.96^2*0.25/A44^2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B45" s="63">
+        <f>CEILING(1.96^2*0.25/A45^2,1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
@@ -1778,6 +2138,7 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -598,6 +598,40 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>The usual choice: 5% margin</v>
+          </tx>
+          <spPr>
+            <a:ln w="16000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sample size calculator'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sample size calculator'!$C$37:$C$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -689,7 +723,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>33</row>
       <rowOff>0</rowOff>
@@ -2019,6 +2053,11 @@
           <t>Sample needed</t>
         </is>
       </c>
+      <c r="C36" s="61" t="inlineStr">
+        <is>
+          <t>At 5% margin</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="62" t="n">
@@ -2028,6 +2067,10 @@
         <f>CEILING(1.96^2*0.25/A37^2,1)</f>
         <v/>
       </c>
+      <c r="C37" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="62" t="n">
@@ -2037,6 +2080,10 @@
         <f>CEILING(1.96^2*0.25/A38^2,1)</f>
         <v/>
       </c>
+      <c r="C38" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="62" t="n">
@@ -2046,6 +2093,10 @@
         <f>CEILING(1.96^2*0.25/A39^2,1)</f>
         <v/>
       </c>
+      <c r="C39" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="62" t="n">
@@ -2055,6 +2106,10 @@
         <f>CEILING(1.96^2*0.25/A40^2,1)</f>
         <v/>
       </c>
+      <c r="C40" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="62" t="n">
@@ -2064,6 +2119,10 @@
         <f>CEILING(1.96^2*0.25/A41^2,1)</f>
         <v/>
       </c>
+      <c r="C41" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="62" t="n">
@@ -2073,6 +2132,10 @@
         <f>CEILING(1.96^2*0.25/A42^2,1)</f>
         <v/>
       </c>
+      <c r="C42" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="62" t="n">
@@ -2082,6 +2145,10 @@
         <f>CEILING(1.96^2*0.25/A43^2,1)</f>
         <v/>
       </c>
+      <c r="C43" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="62" t="n">
@@ -2091,6 +2158,10 @@
         <f>CEILING(1.96^2*0.25/A44^2,1)</f>
         <v/>
       </c>
+      <c r="C44" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="62" t="n">
@@ -2098,6 +2169,10 @@
       </c>
       <c r="B45" s="63">
         <f>CEILING(1.96^2*0.25/A45^2,1)</f>
+        <v/>
+      </c>
+      <c r="C45" s="63">
+        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
         <v/>
       </c>
     </row>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1920,111 +1920,50 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="59" t="inlineStr">
-        <is>
-          <t>How sample size moves with the precision you ask for</t>
-        </is>
-      </c>
+      <c r="A20" s="59" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
-        <is>
-          <t>Worst-case proportion (p=0.5), 95% confidence. Halving the margin of error costs you four times the sample.</t>
-        </is>
-      </c>
+      <c r="A21" s="60" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr">
-        <is>
-          <t>Margin of error</t>
-        </is>
-      </c>
-      <c r="B22" s="61" t="inlineStr">
-        <is>
-          <t>Sample needed</t>
-        </is>
-      </c>
+      <c r="A22" s="61" t="n"/>
+      <c r="B22" s="61" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B23" s="63">
-        <f>CEILING(1.96^2*0.25/A23^2,1)</f>
-        <v/>
-      </c>
+      <c r="A23" s="62" t="n"/>
+      <c r="B23" s="63" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="B24" s="63">
-        <f>CEILING(1.96^2*0.25/A24^2,1)</f>
-        <v/>
-      </c>
+      <c r="A24" s="62" t="n"/>
+      <c r="B24" s="63" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B25" s="63">
-        <f>CEILING(1.96^2*0.25/A25^2,1)</f>
-        <v/>
-      </c>
+      <c r="A25" s="62" t="n"/>
+      <c r="B25" s="63" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="B26" s="63">
-        <f>CEILING(1.96^2*0.25/A26^2,1)</f>
-        <v/>
-      </c>
+      <c r="A26" s="62" t="n"/>
+      <c r="B26" s="63" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="B27" s="63">
-        <f>CEILING(1.96^2*0.25/A27^2,1)</f>
-        <v/>
-      </c>
+      <c r="A27" s="62" t="n"/>
+      <c r="B27" s="63" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="B28" s="63">
-        <f>CEILING(1.96^2*0.25/A28^2,1)</f>
-        <v/>
-      </c>
+      <c r="A28" s="62" t="n"/>
+      <c r="B28" s="63" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="B29" s="63">
-        <f>CEILING(1.96^2*0.25/A29^2,1)</f>
-        <v/>
-      </c>
+      <c r="A29" s="62" t="n"/>
+      <c r="B29" s="63" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="B30" s="63">
-        <f>CEILING(1.96^2*0.25/A30^2,1)</f>
-        <v/>
-      </c>
+      <c r="A30" s="62" t="n"/>
+      <c r="B30" s="63" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B31" s="63">
-        <f>CEILING(1.96^2*0.25/A31^2,1)</f>
-        <v/>
-      </c>
+      <c r="A31" s="62" t="n"/>
+      <c r="B31" s="63" t="n"/>
     </row>
     <row r="32"/>
     <row r="33"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -723,9 +723,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -193,7 +193,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -247,6 +247,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -282,7 +287,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -465,6 +470,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,7 +559,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Sample size against margin of error</a:t>
+              <a:t>Sample size against margin of error — and where your study sits</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -564,7 +572,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Sample needed</v>
+            <v>Sample needed at your alpha and baseline</v>
           </tx>
           <spPr>
             <a:ln w="28000">
@@ -602,19 +610,23 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>The usual choice: 5% margin</v>
+            <v>The change you asked to detect</v>
           </tx>
           <spPr>
-            <a:ln w="16000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="C0392B"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="6"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1580,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="29" min="1" max="1"/>
@@ -1630,7 +1642,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1" s="30">
+    <row r="5" ht="58" customHeight="1" s="30">
       <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Survivorship in CSAT</t>
@@ -1646,8 +1658,16 @@
           <t>Compute the response rate. Compare responder and non-responder profiles on contact reason and outcome.</t>
         </is>
       </c>
-      <c r="D5" s="45" t="n"/>
-      <c r="E5" s="45" t="n"/>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>17% responded. Responders skew heavily to resolved-first-contact (78% of them, against 61% of all contacts), so CSAT 4.4 is the satisfied minority's score and not the population's.</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>Stopped quoting CSAT as a population figure in the charter. Added a 200-contact outbound sample of non-responders each month, and used that as the baseline instead.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1" s="30">
       <c r="A6" s="47" t="inlineStr">
@@ -1743,6 +1763,13 @@
       </c>
       <c r="D10" s="45" t="n"/>
       <c r="E10" s="45" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>How to fill the last two columns. Run the check in column C against your own extract before you write anything — every entry here should be a number you produced, not an impression. WHAT YOU FOUND is the measurement and what it implies for your baseline; ACTION TAKEN is what you changed as a result, because a trap you found and did not act on still contaminates the project. Row 5 is a worked example: delete it and write your own.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1977,7 +2004,7 @@
     <row r="35">
       <c r="A35" s="60" t="inlineStr">
         <is>
-          <t>Worst-case proportion (p=0.5), 95% confidence. Halving the margin of error costs you four times the sample.</t>
+          <t>Your alpha and your baseline rate, from the yellow cells above. Halving the margin of error costs you four times the sample, which is why the last point of precision is the expensive one.</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2021,7 @@
       </c>
       <c r="C36" s="61" t="inlineStr">
         <is>
-          <t>At 5% margin</t>
+          <t>You are here</t>
         </is>
       </c>
     </row>
@@ -2003,11 +2030,11 @@
         <v>0.1</v>
       </c>
       <c r="B37" s="63">
-        <f>CEILING(1.96^2*0.25/A37^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A37^2,1)</f>
         <v/>
       </c>
       <c r="C37" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A37-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A37^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2016,11 +2043,11 @@
         <v>0.075</v>
       </c>
       <c r="B38" s="63">
-        <f>CEILING(1.96^2*0.25/A38^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A38^2,1)</f>
         <v/>
       </c>
       <c r="C38" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A38-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A38^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2029,11 +2056,11 @@
         <v>0.05</v>
       </c>
       <c r="B39" s="63">
-        <f>CEILING(1.96^2*0.25/A39^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A39^2,1)</f>
         <v/>
       </c>
       <c r="C39" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A39-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A39^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2042,11 +2069,11 @@
         <v>0.04</v>
       </c>
       <c r="B40" s="63">
-        <f>CEILING(1.96^2*0.25/A40^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A40^2,1)</f>
         <v/>
       </c>
       <c r="C40" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A40-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A40^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2055,11 +2082,11 @@
         <v>0.03</v>
       </c>
       <c r="B41" s="63">
-        <f>CEILING(1.96^2*0.25/A41^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A41^2,1)</f>
         <v/>
       </c>
       <c r="C41" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A41-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A41^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2068,11 +2095,11 @@
         <v>0.025</v>
       </c>
       <c r="B42" s="63">
-        <f>CEILING(1.96^2*0.25/A42^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A42^2,1)</f>
         <v/>
       </c>
       <c r="C42" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A42-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A42^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2081,11 +2108,11 @@
         <v>0.02</v>
       </c>
       <c r="B43" s="63">
-        <f>CEILING(1.96^2*0.25/A43^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A43^2,1)</f>
         <v/>
       </c>
       <c r="C43" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A43-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A43^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2094,11 +2121,11 @@
         <v>0.015</v>
       </c>
       <c r="B44" s="63">
-        <f>CEILING(1.96^2*0.25/A44^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A44^2,1)</f>
         <v/>
       </c>
       <c r="C44" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A44-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A44^2,1),NA())</f>
         <v/>
       </c>
     </row>
@@ -2107,11 +2134,11 @@
         <v>0.01</v>
       </c>
       <c r="B45" s="63">
-        <f>CEILING(1.96^2*0.25/A45^2,1)</f>
+        <f>CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A45^2,1)</f>
         <v/>
       </c>
       <c r="C45" s="63">
-        <f>CEILING(1.96^2*0.25/0.05^2,1)</f>
+        <f>IF(ABS(A45-$C$6)&lt;=0.0051,CEILING(IFERROR(NORMSINV(1-$C$7/2),1.96)^2*IF(AND($C$5&gt;0,$C$5&lt;1),$C$5*(1-$C$5),0.25)/A45^2,1),NA())</f>
         <v/>
       </c>
     </row>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1088,6 +1088,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="30">
       <c r="A4" s="38" t="inlineStr">
         <is>
@@ -1131,6 +1132,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="31.5" customHeight="1" s="30">
       <c r="A9" s="43" t="inlineStr">
         <is>
@@ -1545,6 +1547,7 @@
       <c r="O24" s="45" t="n"/>
       <c r="P24" s="45" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="30">
       <c r="A26" s="38" t="inlineStr">
         <is>
@@ -1615,6 +1618,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="30">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -1764,6 +1768,7 @@
       <c r="D10" s="45" t="n"/>
       <c r="E10" s="45" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
         <is>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -193,7 +193,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -252,6 +252,11 @@
         <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -287,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -472,6 +477,15 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1123,12 +1137,12 @@
     <row r="7" ht="15" customHeight="1" s="30">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1230,80 @@
       </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="30">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>7-day reopen rate</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>Proportion</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>Zendesk</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>Warehouse query, saved as reopen_v2.sql</t>
         </is>
       </c>
-      <c r="E10" s="44" t="inlineStr">
+      <c r="E10" s="67" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="F10" s="44" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>All billing tickets first resolved in the window</t>
         </is>
       </c>
-      <c r="G10" s="44" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr">
         <is>
           <t>2026-01-01 to 2026-03-31</t>
         </is>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="67" t="n">
         <v>61400</v>
       </c>
-      <c r="I10" s="44" t="inlineStr">
+      <c r="I10" s="67" t="inlineStr">
         <is>
           <t>Full population, no sampling needed</t>
         </is>
       </c>
-      <c r="J10" s="44" t="inlineStr">
+      <c r="J10" s="67" t="inlineStr">
         <is>
           <t>Census</t>
         </is>
       </c>
-      <c r="K10" s="44" t="inlineStr">
+      <c r="K10" s="67" t="inlineStr">
         <is>
           <t>Contact reason, tenure band, channel, site</t>
         </is>
       </c>
-      <c r="L10" s="44" t="inlineStr">
+      <c r="L10" s="67" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="M10" s="44" t="inlineStr">
+      <c r="M10" s="67" t="inlineStr">
         <is>
           <t>Weekly Monday</t>
         </is>
       </c>
-      <c r="N10" s="44" t="inlineStr">
+      <c r="N10" s="67" t="inlineStr">
         <is>
           <t>warehouse + immutable snapshot</t>
         </is>
       </c>
-      <c r="O10" s="44" t="inlineStr">
+      <c r="O10" s="67" t="inlineStr">
         <is>
           <t>Reconcile total to the ops dashboard</t>
         </is>
       </c>
-      <c r="P10" s="44" t="inlineStr">
+      <c r="P10" s="67" t="inlineStr">
         <is>
           <t>M. Berenji</t>
         </is>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -292,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -486,6 +486,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1616,6 +1619,7 @@
     <col width="44" customWidth="1" style="29" min="2" max="2"/>
     <col width="52" customWidth="1" style="29" min="3" max="3"/>
     <col width="34" customWidth="1" style="29" min="4" max="5"/>
+    <col width="13" customWidth="1" style="30" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="30">
@@ -1783,17 +1787,18 @@
       <c r="E10" s="45" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+    <row r="12" ht="39" customHeight="1" s="30">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>How to fill the last two columns. Run the check in column C against your own extract before you write anything — every entry here should be a number you produced, not an impression. WHAT YOU FOUND is the measurement and what it implies for your baseline; ACTION TAKEN is what you changed as a result, because a trap you found and did not act on still contaminates the project. Row 5 is a worked example: delete it and write your own.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1664,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1" s="30">
+    <row r="5" ht="182" customHeight="1" s="30">
       <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Survivorship in CSAT</t>
@@ -1795,10 +1795,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="E5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2025,8 +2026,8 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+    <row r="35" ht="26" customHeight="1" s="30">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>Your alpha and your baseline rate, from the yellow cells above. Halving the margin of error costs you four times the sample, which is why the last point of precision is the expensive one.</t>
         </is>
@@ -2167,9 +2168,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A10:B10"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1664,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="182" customHeight="1" s="30">
+    <row r="5" ht="58" customHeight="1" s="30">
       <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Survivorship in CSAT</t>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -2029,7 +2029,7 @@
     <row r="35" ht="26" customHeight="1" s="30">
       <c r="A35" s="68" t="inlineStr">
         <is>
-          <t>Your alpha and your baseline rate, from the yellow cells above. Halving the margin of error costs you four times the sample, which is why the last point of precision is the expensive one.</t>
+          <t>Your alpha and your baseline rate, from the yellow cells above. Halving the margin of error costs you four times the sample, which is why the last point of precision is the expensive one. Nothing in this block is for you to fill in, and YOU ARE HERE is blank on every row but the margin of error you asked for — that one point is the marker sitting on the curve.</t>
         </is>
       </c>
     </row>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -292,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -489,6 +489,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1149,7 +1152,13 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8" ht="36" customHeight="1" s="30">
+      <c r="A8" s="69" t="inlineStr">
+        <is>
+          <t>Key: Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="31.5" customHeight="1" s="30">
       <c r="A9" s="43" t="inlineStr">
         <is>
@@ -1580,11 +1589,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A8:P8"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A26:P26"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1152,10 +1152,12 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="30">
+    <row r="8" ht="84" customHeight="1" s="30">
       <c r="A8" s="69" t="inlineStr">
         <is>
-          <t>Key: Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
+          <t xml:space="preserve">  ·  Key:
+• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
+• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
         </is>
       </c>
     </row>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -190,6 +190,11 @@
     <font>
       <i val="1"/>
       <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -292,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -492,6 +497,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -755,7 +763,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1152,10 +1160,12 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="84" customHeight="1" s="30">
+    <row r="8" ht="156" customHeight="1" s="30">
       <c r="A8" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
+• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
+• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
 • Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
 • Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
         </is>
@@ -1825,13 +1835,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="29" min="1" max="1"/>
     <col width="18" customWidth="1" style="29" min="2" max="2"/>
     <col width="16" customWidth="1" style="29" min="3" max="3"/>
     <col width="68" customWidth="1" style="29" min="4" max="4"/>
+    <col width="13" customWidth="1" style="30" min="5" max="5"/>
+    <col width="13" customWidth="1" style="30" min="6" max="6"/>
+    <col width="13" customWidth="1" style="30" min="7" max="7"/>
+    <col width="13" customWidth="1" style="30" min="8" max="8"/>
+    <col width="13" customWidth="1" style="30" min="9" max="9"/>
+    <col width="13" customWidth="1" style="30" min="10" max="10"/>
+    <col width="13" customWidth="1" style="30" min="11" max="11"/>
+    <col width="13" customWidth="1" style="30" min="12" max="12"/>
+    <col width="13" customWidth="1" style="30" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="30">
@@ -2179,8 +2198,22 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52" ht="77" customHeight="1" s="30">
+      <c r="E52" s="70" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Read down, not across: halving the margin of error roughly quadruples the sample. The marked point is your own study. If it sits on the steep left-hand part of the curve, a small change in the precision you ask for costs you a lot of tickets — decide the margin you actually need before you commit to a duration.
+SO:  Fix the margin of error first, then read the sample off the curve and let it set the duration. Sizing the other way round — picking a duration and accepting whatever precision falls out — is how a pilot ends up unable to answer its own question.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A35:D35"/>
@@ -2188,6 +2221,7 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E52:M52"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:D2"/>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1160,13 +1160,10 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="156" customHeight="1" s="30">
+    <row r="8" ht="48" customHeight="1" s="30">
       <c r="A8" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
-• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
-• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things  ·  Key:
 • Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
         </is>
       </c>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -499,6 +499,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,8 +1046,20 @@
     </row>
     <row r="14"/>
     <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="16" ht="26" customHeight="1" s="30">
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1" s="30">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -1069,6 +1084,10 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1160,11 +1179,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" s="30">
+    <row r="8" ht="24" customHeight="1" s="30">
       <c r="A8" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day. Getting it wrong is the most expensive mistake on this sheet: a rate counted per contact and a rate counted per issue are different numbers with the same name, which is how one measurement ends up meaning two things</t>
+• Unit of analysis = the thing one row of your data IS — a contact, an issue, a customer, an agent-day.</t>
         </is>
       </c>
     </row>

--- a/templates/05-data-collection-plan.xlsx
+++ b/templates/05-data-collection-plan.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G10" s="67" t="inlineStr">
         <is>
-          <t>2026-01-01 to 2026-03-31</t>
+          <t>2026-01-05 to 2026-03-29</t>
         </is>
       </c>
       <c r="H10" s="67" t="n">
